--- a/UNICEF_Lebanon.xlsx
+++ b/UNICEF_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -492,6 +492,598 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UNICEF Executive Director calls for children to be protected and placed at the heart of Lebanon’s recovery</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/unicef-executive-director-calls-children-be-protected-and-placed-heart-lebanons</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UNICEF Executive Director calls for children to be protected and placed at the heart of Lebanon’s recovery
+- English
+- العربية
+Beirut/New York, 2 October 2026 – UNICEF Executive Director Catherine Russell concluded a visit to Lebanon today, calling for urgent action to protect children from the ongoing impact of conflict and economic crisis and to place their rights and needs at the centre of the country’s recovery.
+Russell visited southern Lebanon and Beirut, and met children and families whose lives have been upended by violence and displacement. At a collective shelter in Tyre, she met families who had fled their homes, some more than once, including a mother caring for her newborn. She also spoke with children whose homes and schools have been damaged or destroyed, and who remain unsure of when they will be able to return.
+“Economic hardship and the impact of conflict continue to devastate the lives of children and families in Lebanon,” said Russell. “Children in Lebanon have lived through years of overlapping crises. They cannot afford to lose more of their childhood. Investing in children is the best road to recovery.”
+Russell visited a UNICEF-supported Makani centre, where she met children and young people accessing learning, psychosocial support and other services that are helping them cope with the ongoing crisis.
+The recent conflict has had a devastating impact on children. Since 2 March, 2026, at least 261 children have been killed and 1,056 injured. Some 436 schools have been damaged or destroyed, leaving around 100,000 children at risk of being without a classroom.
+In Beirut, Russell met with H.E. President Joseph Aoun, Prime Minister Dr. Nawaf Salam and the Minister of Social Affairs, Haneen Sayed. Discussions focused on the situation of children and ensuring that children are healthy, educated and protected.
+UNICEF continues to work alongside the Government of Lebanon and partners to respond to urgent humanitarian needs while sustaining the national systems and services children depend on.
+Since the beginning of 2026, UNICEF has intensified its humanitarian response. That includes supporting injured children and displaced families and delivering essential supplies to shelters and health facilities. UNICEF is also helping children access learning and psychosocial support.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:28.845399+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Four in five households in Lebanon struggle to afford basic needs as conflict deepens deprivation for children – UNICEF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/four-five-households-lebanon-struggle-afford-basic-needs-conflict-deepens</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Four in five households in Lebanon struggle to afford basic needs as conflict deepens deprivation for children – UNICEF
+New UNICEF assessment finds children going hungry, missing health care and education, and experiencing widespread psychological distress
+- English
+- العربية
+BEIRUT, 30 September 2026 – Four in five households in Lebanon are struggling to afford basic necessities as conflict compounds years of economic crisis, pushing children into hunger, out of education and into work, UNICEF warned today.
+A new UNICEF report, An Enduring Nightmare, reveals the mounting toll on children and young people across Lebanon. More than one in five households surveyed - 22 per cent - reported that their children had gone to bed hungry and ten per cent of households with children under five can provide a sufficiently nutritious diet while 31 per cent said children had gone without needed health care, mainly because families could not afford it. Fourteen per cent reported at least one child working – more than twice the proportion recorded in January 2025.
+“Children and young people in Lebanon are being asked to bear a burden no child should have to carry,” said UNICEF Lebanon Representative Marcoluigi Corsi. “Families are being pushed to the brink, while children are missing health care and education, being pushed into work and experiencing profound psychological distress. Without urgent and sustained action, these pressures are shaping their lives for years to come”.
+The conflict has taken a devastating toll on children. Since 2 March 2026, at least 261 children have been killed and 1,056 injured – an average of seven children killed or injured every day over six months. An estimated 12 per cent of injured children are now living with a disability.
+Children’s education has also been severely disrupted. Some 436 schools have been damaged or destroyed, leaving around 100,000 children at risk of being without a classroom, while 86 teachers have been killed or injured. At household level, 46 per cent reported cutting education spending and 17 per cent said their children had to stop attending school. Among children attending school, 29 per cent were unable to learn as expected, often because of difficulty concentrating and emotional distress.
+Beyond the visible destruction, the psychological toll is also profound. An estimated 770,000 children have experienced psychological distress over the past six months. More than half of households said their children’s emotional well-being had worsened, while almost two-thirds - 63 per cent - reported that their children were anxious or nervous.
+Young people in Lebanon also face shrinking opportunities. An earlier UNICEF assessment this year found that only 22 per cent of young people aged 18–25 were in school or university, largely because of financial barriers, while at the time of the survey, 67 per cent were unemployed. The findings point to the growing challenges young people face in continuing their education, accessing services and building their futures in Lebanon.
+UNICEF continues to respond to urgent humanitarian needs, including through supporting the national systems and services children and families depend on. Since January 2026, UNICEF has intensified its efforts to address humanitarian needs, treating injured children, delivering supplies to shelters and medical facilities, and providing care to displaced families.
+“Without urgent and sustained action, an entire generation of children and young people risks carrying the scars of this crisis into adulthood,” said Corsi. “Lebanon’s recovery depends on protecting children now and upholding their right to health care, education, protection and the opportunities they need to build their futures.”
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:30.528681+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Salam: “Lebanon’s Recovery Cannot Succeed Without Education.”</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/salam-lebanons-recovery-cannot-succeed-without-education</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Salam: “Lebanon’s Recovery Cannot Succeed Without Education.”
+Lebanon reaffirms commitment to education recovery and reform, placing learning at the heart of the country’s future
+- English
+- العربية
+16 September 2026, Beirut – Under the patronage of Prime Minister, the Ministry of Education and Higher Education (MEHE) today convened the third High-Level Strategic Management Board of the Transition and Resilience Education Fund (TREF), bringing together the Government of Lebanon, contributing partners and UNICEF to advance education recovery and to support strategic direction for the 2026/2027 school year and beyond.
+The meeting comes at a critical moment for education in Lebanon. Following another year of conflict and disruption, the focus is on restoring safe learning environments, recovering lost learning and ensuring that the most vulnerable children remain connected to education, while sustaining reforms that improve learning, inclusion, accountability and the performance of the education system.
+Established under MEHE’s leadership, TREF brings together contributing partners - the European Union, Germany through KfW, France through AFD, Switzerland, the United Kingdom, the Netherlands, Finland Norway, the Abdulla Al Ghurair Foundation, Akelius Foundation, and UNICEF - around Lebanon’s national education priorities. Their sustained partnership has enabled TREF to protect learning through successive crises while supporting reforms to strengthen the public education system.
+The Lebanese Prime Minister Dr. Nawaf Salam said: “Education is central to Lebanon’s recovery and to the future we want to build for our children. After successive crises have disrupted learning and placed enormous pressure on the education system, it is our responsibility to ensure that children recover the learning they have lost. Yet, even under these exceptional and difficult circumstances, education did not stop. The Ministry of Education and Higher Education, together with teachers, school administrations and partners, has worked tirelessly to keep children connected to their schools and safeguard their right to learn. On behalf of the Government of Lebanon, I reiterate our support to the Ministry of Education and Higher Education and our commitment to advancing the implementation of Vision 2040. The Government remains committed to carrying forward the reforms and national investments this requires, with the support of our international partners.”
+Minister of Education and Higher Education Dr Rima Karami said: “Our priority is to ensure that every child returns not only to school, but to meaningful learning. As we restore learning after another year of disruption, we are also continuing the reforms needed to strengthen the public education system for the long term. Through our Strategic Vision for Educational Renewal 2025–2040, we are investing in better teaching and learning, more inclusive schools, stronger governance and clearer pathways for children who are outside education. Recovery and reform must move forward together, so that every investment we make today delivers better and more equitable outcomes for learners.”
+Renewed hostilities in 2026 displaced more than one million people, including 390,000 children, while schools were closed, damaged or used as shelters. A nationwide initial assessment found 340 schools damaged or destroyed, putting thousands of children at risk of starting the new school year without a classroom.
+Learning recovery is now at the forefront of efforts for the new school year. Restoring damaged schools, strengthening foundational literacy and numeracy, supporting teachers and helping children regain lost learning will be critical to ensuring that returning to school also means returning to meaningful learning.
+"The European Union remains committed to supporting Lebanon's public education system and the Ministry's vision for education recovery,” said Samy Saadi, Chargé d’Affaires a.i of the European Union Delegation to Lebanon. “Education has paid a severe toll during the recent conflict, with significant disruption to learning and damage to schools. Through the Transition and Resilience Education Fund, our support has helped restore safe learning environments and ensure that every child can access quality education. Looking ahead, our priority is to continue strengthening the Ministry's institutional capacity, while encouraging more investment from Lebanon's own resources, to ensure that progress on reforms is embedded within the Ministry and can outlast donor funding."
+“Every disruption to education risks widening learning gaps and pushing the most vulnerable children further behind,” said Marcoluigi Corsi, UNICEF Representative in Lebanon. “With the sustained support of TREF contributing partners, UNICEF will continue working alongside MEHE to accelerate learning recovery, restore safe schools and sustain reforms that translate investment into better outcomes for children. Investing in education recovery and reform is ultimately an investment in Lebanon’s children, its human capital and its future.”
+The Transition and Resilience Education Fund (TREF) Strategic Management Board reaffirmed its commitment to sustaining learning while strengthening Lebanon’s education system for the longer term. Building on the progress achieved, TREF will continue supporting MEHE to turn education recovery into improved learning outcomes, expand opportunities for children most at risk of being left behind including Out of School Children, and strengthen the systems, governance and use of financing needed to deliver quality and inclusive education.
+Since its establishment in 2022, TREF has provided a platform for multi-year partnership between MEHE, contributing partners and UNICEF, combining international financing with technical assistance at national, regional, school, classroom and community levels.
+Through this partnership, TREF supports Lebanon’s efforts to build an education system that is more equitable, effective and resilient, and capable of delivering for every child.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:32.243102+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lebanon’s Young People Are Not Losing Hope. They Are Losing Opportunities, and Lebanon Risks Losing Its Future.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/lebanons-young-people-are-not-losing-hope-they-are-losing-opportunities-and-lebanon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lebanon’s Young People Are Not Losing Hope. They Are Losing Opportunities, and Lebanon Risks Losing Its Future.
+OpEd By Marcoluigi Corsi, UNICEF representative in Lebanon
+- English
+- العربية
+“Every generation faces defining moments. For Lebanon’s young people, those moments have become their everyday reality.
+They have grown up through years of overlapping crises and for many, instability has become the backdrop of their adolescence and early adulthood. Yet resilience alone cannot replace opportunity.
+Lebanon is a young country. Approximately 44 per cent of its estimated six million people are under the age of 24, making young people one of the country’s greatest assets and most important investments for the future.
+Yet even before the latest escalation, young people were already facing significant barriers to building secure and fulfilling their lives. In 2022, youth unemployment reached 47.8 per cent—more than double the national average—driven by economic collapse, currency devaluation and widespread business closures. Young women faced greater obstacles, with nearly one third not engaged in employment, education or training.
+Today, the transition from education to employment, from dependence to independence, and from uncertainty to hope, has become increasingly difficult.
+A recent UNICEF assessment among surveyed young people aged 18–29 years found that nearly all (95.4 %) reported feeling sometimes sad or depressed. This reflects not only a mental health concern, but the emotional toll of prolonged crisis and uncertainty, financial pressure and repeated shocks. Behind these figures are young people carrying family responsibilities while struggling to imagine a stable future.
+Education, previously one of Lebanon’s strongest foundations, is also under strain. Only 22.2 % of young respondents are currently attending school or university, with financial barriers cited as the main obstacle.
+The challenges are deeply interconnected. Economic hardship limits access to education. Interrupted learning reduces employment prospects. Unemployment increases psychological distress. Exposure to conflict and instability compounds these pressures. Without integrated action, these pressures will continue to reinforce one another.
+The data point to exactly where action is needed. Nearly 80 per cent of young people say cash assistance is their most urgent need, while more than four in five say they cannot afford school or university costs.
+Young people need sustained financial support, affordable access to education and training, safe pathways to decent work, and dedicated mental health and psychosocial services that respond to their specific needs.
+These investments are not only humanitarian priorities—they are essential for Lebanon’s recovery. Young people are not passive recipients of assistance. Across the country, they continue to support their families, volunteer in their communities and create solutions despite immense challenges. Given the opportunity, they can drive innovation, strengthen social cohesion and contribute to economic recovery.
+Perhaps the most hopeful finding in this: although more than half of surveyed young people say they intend to migrate, nearly 69 per cent say they would stay in Lebanon if conditions improved.
+Young people are not turning away from their country. They are searching for opportunities that will allow them to build their future at home.
+As Lebanon marks International Youth Day, that is the test facing the Lebanese government and every donor conference.
+UNICEF Lebanon is ready to work with the Government and partners to deliver at the scale this generation needs. What happens next will be decided not by what young people are willing to endure, but by whether Lebanon and the international community invest in the opportunities, services and support they need to build their future at home.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:33.946971+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lebanese Ministry of Public Health and UNICEF launch National Breastfeeding Campaign and IYCF Capacity Building Programme</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/lebanese-ministry-public-health-and-unicef-launch-national-breastfeeding-campaign</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lebanese Ministry of Public Health and UNICEF launch National Breastfeeding Campaign and IYCF Capacity Building Programme
+- English
+- العربية
+Beirut, 3 August 2026 – On the occasion of World Breastfeeding Week, the Ministry of Public Health, in partnership with UNICEF, and in collaboration with the World Health Organization (WHO), the World Bank and partners, launched the National campaign on Breastfeeding and the Infant and Young Child Feeding (IYCF) Capacity Building Programme.
+The launch highlights Lebanon’s commitment to strengthening support for breastfeeding and improving infant and young child feeding practices, recognizing their essential role in children’s survival, growth, development and long-term health.
+the Minster of Public Health Dr. Rakan Nassereldine said: "We, at the Ministry of Public Health, reaffirm our commitment to advancing national programmes that promote the health of mothers and children. We firmly believe that investing in nutrition during the earliest stages of life is an investment in healthier children, stronger communities, and a healthier, more prosperous future for our nation."
+The newly launched Community Infant and Young Child Feeding Package, alongside the updated IYCF training toolkit and complementary feeding guidance , will equip, caregivers, frontline health workers and health professionals, with practical knowledge and skills to provide quality, evidence-based counselling and support to mothers, caregivers and families across hospitals, primary health care centres and communities.
+“Today’s launch goes beyond raising awareness; it strengthens the systems and capacities that will continue supporting children and families for years to come” said Marcoluigi Corsi, UNICEF Representative in Lebanon “UNICEF is proud to support the Ministry of Public Health and partners in advancing quality infant and young child feeding services across Lebanon, giving every child the best possible start in life.”
+“Good nutrition in the first two years of life shapes a child's entire future, their growth, their brain development, their ability to learn," said Dr Yutaro Setoya, WHO Deputy Representative in Lebanon. "This new complementary feeding guidance gives health workers across Lebanon the tools to support families with accurate, consistent advice at exactly the moments it matters most. WHO remains committed to working alongside the Ministry of Public Health and our partners to make sure every child in Lebanon gets the healthy start they deserve.
+“Investing in child nutrition is an investment in Lebanon’s human capital. The first years of life are a critical window for building the foundations of health, learning, and future productivity. The World Bank is proud to support this training toolkit, which equips healthcare workers with practical skills to provide quality nutrition support and help give children the strongest possible start in life” Said Mouna Couzi, World Bank Representative in Lebanon.
+The National IYCF Capacity Building Programme aims to strengthen the skills of health professionals and community-based workers, ensuring that families receive consistent and appropriate quality support on breastfeeding and complementary feeding. The Program contributes to building stronger foundation for quality nutrition services and better health system that enable pregnant women, parents, and caregivers to make informed feeding and care choices, particularly during the child’s first 1,000 days, a critical window when good nutrition, responsive caregiving and early stimulation lay the foundation for healthy growth, brain development, learning and lifelong well-being.
+Through this collaboration, the Ministry of Public Health, WHO, the World Bank, UNICEF and partners continue working to strengthen Lebanon’s health and nutrition systems and advance the well-being of every child.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:35.629048+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>At least 100,000 children risk missing the next school year without urgent action to restore Lebanon's schools</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/least%E2%80%AF100000-children%E2%80%AFrisk-missing-next-school-year-without-urgent-action-restore</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>At least 100,000 children risk missing the next school year without urgent action to restore Lebanon's schools
+Nationwide assessment reveals 340 schools damaged or destroyed, placing children's learning, protection and recovery at risk.
+- English
+- العربية
+BEIRUT, 2 July 2026 – At least 100,000 children in Lebanon could be left without a classroom when the next academic year begins, unless urgent action is taken before September to repair and restore schools damaged by the recent conflict.
+A comprehensive nationwide assessment conducted by the Ministry of Education and Higher Education in June has revealed the devastating impact caused by the recent conflict to Lebanon's education system. The assessment found that 340 public, private and Technical and Vocational Education and Training (TVET) schools have been damaged, including 17 schools that have been completely destroyed.
+The assessment was developed with technical support from UNICEF through the Transition and Resilience Education Fund (TREF), supported by the European Union, Germany, France and Switzerland.
+The damage spans many of the governorates most affected by the conflict, including Nabatiyeh, South Lebanon, Bekaa, Baalbek-Hermel, Beirut and Mount Lebanon. While some schools sustained minor damage, many require extensive rehabilitation or complete reconstruction before they can safely welcome students and teachers back.
+"Schools are far more than buildings," said UNICEF Representative in Lebanon Marcoluigi Corsi. "They are places where children learn, feel safe, and begin to recover from crisis. This assessment provides the first comprehensive picture of the scale of damage to Lebanon's education system. With the new school year approaching, urgent investment is needed to rehabilitate damaged schools and ensure children can return to learning without delay.”
+The findings come after years of repeated disruption to children's education in Lebanon, driven by overlapping crises and conflict. For many children, another prolonged interruption to learning would carry lasting consequences for their education, wellbeing, mental health, and future opportunities. The lack of access to education also increases their vulnerability to protection risks, such as early marriage and child labor.
+"Every day a child remains out of school, the risk of learning loss and dropping out increases," said Corsi. "Education cannot wait for recovery to begin; it is an essential part of recovery. Rehabilitating schools goes beyond repairing walls and classrooms, it restores hope and provides protection, giving every child the chance to learn and build their future."
+UNICEF is working alongside the Ministry of Education and Higher Education, donors and partners to support school rehabilitation, learning continuity and education recovery across Lebanon. While TREF donors have been significantly supporting the education sector for years, the scale of destruction requires significantly increased investment, to restore safe learning environments before the start of the next academic year.
+Every child has the right to learn in a safe, protective and inclusive environment. Investing in education recovery today is an investment in Lebanon's children, its communities and its future.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:37.344039+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Statement by UNICEF Country Representative in Lebanon, Marcoluigi Corsi, on the ongoing suffering of children in Lebanon over 100 days into conflict</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/statement-unicef-country-representative-lebanon-marcoluigi-corsi-ongoing-suffering</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Statement by UNICEF Country Representative in Lebanon, Marcoluigi Corsi, on the ongoing suffering of children in Lebanon over 100 days into conflict
+With renewed hope for an end to hostilities, children need more than an end to violence, they need protection, wellbeing, and a safer future.
+- English
+- العربية
+BEIRUT, 17 June 2026- “For more than three months, children in Lebanon have lived through experiences no child should ever endure. Many have fled their homes multiple times, witnessed violence first-hand, lost loved ones, and seen their schools, communities, and sense of safety shattered.
+“After over 100 days of increased hostilities - since 2 March - 247 children have been killed and 992 injured, an average of 12 children killed or maimed every day. Behind these staggering figures are lives cut short or forever changed, and families facing profound loss, trauma, and uncertainty.
+"The numbers alone cannot convey the full scale of the crisis. Beyond those killed and maimed, an entire generation of children has seen its childhood disrupted. Their sense of safety – one that every child needs to grow and thrive – remains profoundly undermined.
+“With renewed hope for hostilities to halt, children need more than an end to violence - they require protection, sustained support to restore access to essential services, and to be offered a consistent pathway to recovery and a safer future.
+“Widespread destruction remains across large parts of the country, affecting homes, schools, and essential services - including water, sanitation and hygiene systems - further compounding already severe humanitarian needs.
+“More than 770,000 children are experiencing heightened distress from repeated exposure to violence, loss and displacement. Many remain unable to return home because of ongoing fighting and the threat of unexploded ordnance.
+“The scale of physical and psychological harm we are witnessing is unacceptable, and children continue to pay a terrible price for this conflict. Ending the violence is essential to restore access to education and other basic services and provide children with a pathway to recovery and a safer future. The true cost of this crisis will not only be measured in lives lost today, but in the opportunities missed tomorrow. Without sustained support, many children risk carrying the consequences of this war with them for years to come."
+“UNICEF reiterates its urgent call for a sustained cessation of hostilities. Children need to be protected from further harm and schools, hospitals, water systems and other civilian infrastructure urgently safeguarded. Humanitarian access must be ensured and international law must be respected.
+“Most importantly, Lebanon's children must be given the chance not only to survive this crisis, but to recover from it and reclaim the future that conflict has placed at risk."
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:39.043510+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>The Ministry of Education and Higher Education inaugurated Kfarzabad Secondary Public School in partnership with UNICEF with the support of France, advancing access to quality and inclusive education</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/ministry-education-and-higher-education-inaugurated-kfarzabad-secondary-public</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Ministry of Education and Higher Education inaugurated Kfarzabad Secondary Public School in partnership with UNICEF with the support of France, advancing access to quality and inclusive education
+- English
+- العربية
+15 June 2026 – The Ministry of Education and Higher Education (MEHE), in partnership with France and UNICEF, inaugurated today the newly constructed Kfarzabad Secondary School in the Bekaa, marking an important milestone in expanding access to quality, inclusive and uninterrupted education for children and young people in Lebanon.
+Constructed by UNICEF with the generous support of France over a period of approximately two and a half years, the school provides a modern, safe and sustainable learning environment for students. The facility includes classrooms alongside a range of dedicated pedagogical spaces, including laboratories, workshops, art and music rooms, a library, a multipurpose hall, and a playground, in addition to administrative offices and service buildings. The campus is further complemented by landscaped outdoor areas, sports and recreational grounds, and parking facilities.
+Minister of Education and Higher Education Dr. Rima Karami said: “Standing here today, in circumstances we all know too well, to inaugurate a new public secondary school is in itself a statement. It is a statement that the state is still capable of building, that public education is worth investing in, and that our children deserve our continued commitment, whatever the circumstances. At the Ministry of Education and Higher Education, we are working today with a clear vision for the education sector. Our first and foremost goal is to ensure quality and equitable education for every child in Lebanon, without exception and without discrimination”.
+At a time when Lebanon’s education system continues to face significant challenges, including repeated disruptions to learning due to overlapping crises and conflict, investments in public school infrastructure remain essential. Safe, resilient and inclusive schools not only support continuity of learning but also provide children and adolescents with stability, protection and opportunities to build their future. Expanding and improving school facilities is critical to supporting continuity of learning, strengthening resilience, and ensuring that no child is left behind.
+“My presence here today reflects the enduring commitment of France to stand alongside Lebanon,” said Herve Magro, Ambassador of France to Lebanon. “In times of progress as well as in periods of hardship, France remains fully mobilized, deploying the full range of its diplomatic, political, humanitarian and development instruments to support the Lebanese people and strengthen national institutions”.
+“The inauguration of Kfarzabad Secondary School is an important investment in Lebanon’s public education system and in the future of its children and adolescents,” said Marcoluigi Corsi, UNICEF Representative in Lebanon. “At a time when many students have experienced repeated disruptions to their learning, expanding access to safe, inclusive and quality education remains essential. We are grateful to France for its longstanding partnership and commitment to education in Lebanon. This investment will help provide children and adolescents with a safe and supportive learning environment where they can learn and thrive. UNICEF remains committed to supporting the Ministry of Education and Higher Education and partners to ensure uninterrupted, quality education for every child in Lebanon.”
+The school has been designed in line with sustainable and resilient building principles, integrating environmentally friendly systems that improve resource efficiency and reduce operational costs. These include a solar hot water system, a rainwater harvesting system, a sewage treatment plant for irrigation purposes, and a reverse osmosis water treatment system. Enhanced thermal insulation and the use of low-emission materials contribute to improved comfort and healthier indoor environments for students and teachers.
+To further strengthen energy resilience, the school is equipped with a 34 kWp solar photovoltaic system, supported by the Agence Française de Développement (AFD), reducing dependence on the national electricity grid and ensuring continuity of learning. The facility is also fully accessible to children with disabilities, with ramps, an elevator and adapted sanitation facilities, promoting inclusive education for all.
+Building on this commitment, AFD has also supported the procurement and installation of school furniture, ensuring that all learning spaces are fully equipped and ready for use. With the completion of furniture installation and solarization works, the school is now fully operational and well positioned to provide a conducive and resilient learning environment for students and teachers for years to come.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:43.223495+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>At least 59 children reportedly killed or injured in Lebanon in the past week despite ceasefire - UNICEF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/least-59-children-reportedly-killed-or-injured-lebanon-past-week-despite-ceasefir</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>At least 59 children reportedly killed or injured in Lebanon in the past week despite ceasefire - UNICEF
+Ongoing violence and displacement pushing over 770,000 children towards chronic mental health conditions
+- English
+- العربية
+AMMAN/BEIRUT, 13 May 2026 – Children in Lebanon continue to be at the sharp end of ongoing violence, displacement and exposure to traumatic events. In the past seven days alone, despite an agreed ceasefire on 17 April 2026, at least 59 children have reportedly been killed or injured. This includes two children from the same family who were killed this morning, along with their mother, in a strike that hit their car – a stark reminder of the ongoing risks children continue to face.
+In total, at least 23 children have been killed and 93 injured since the ceasefire, according to the Ministry of Public Health, and brings the total to 200 children killed and 806 injured since 2 March, the equivalent of nearly 14 children killed or injured every day.
+“Children are being killed and injured when they should be returning to classrooms, playing with friends, and recovering from months of fear and upheaval,” said UNICEF Regional Director for the Middle East and North Africa, Edouard Beigbeder. “Nearly a month ago, an agreement was reached to silence the weapons and stop the violence. Reality is proving to be very different. Continued attacks are killing and injuring children, deepening their exposure to trauma and leaving devastating consequences that could last a lifetime.”
+Beyond the immediate impact of bombs and airstrikes, an estimated 770,000 children are experiencing heightened distress from repeated exposure to violence, loss and displacement. Children and caregivers report symptoms linked to traumatic stress and grief, including extreme fear and worry, nightmares, sleeplessness and feelings of hopelessness. Without mental health and psychosocial support in safe and secure settings, these children are at serious risk of developing chronic or lifelong mental health issues.
+Evidence from UNICEF’s 2025 Child-focused Rapid Assessment (CfRA) already pointed to a sharp deterioration in children’s mental health following the 2024 military escalation, with 72 per cent of caregivers reporting their children were anxious or nervous and 62 per cent depressed or sad. Continued violence and instability have since deepened these impacts, leaving children without the time, safety, or support needed to recover.
+“The impact of repeated exposure to conflict on children’s mental health can be profound and long-lasting,” said Beigbeder. “Children in Lebanon have endured waves of violence, displacement, and uncertainty, often with little or no time to recover. Without urgent support, the psychological scars of this compounded crisis may stay with them for years, affecting not only their wellbeing, but their future and the future of the country.”
+Urgent investment in mental health services and psychosocial support services is critical to help children recover from the psychological impact of conflict and prevent long-term harm. UNICEF is scaling up mental health and psychosocial support services across Lebanon, including through safe spaces and community-based programmes. However, needs continue to far outpace available resources.
+UNICEF is calling on all parties to protect children, uphold international humanitarian law, and take all necessary measures to ensure that the ceasefire holds.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:44.923211+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>The Republic of Korea announce a new contribution to support UNICEF’s emergency response for children in Lebanon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/republic-korea-announce-new-contribution-support-unicefs-emergency-response-children</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The Republic of Korea announce a new contribution to support UNICEF’s emergency response for children in Lebanon
+- English
+- العربية
+Beirut, 30 April 2026 – As the crisis in Lebanon continues to affect children and families, the Government of the Republic of Korea has contributed US$1 million to UNICEF to support emergency education and nutrition interventions.
+This timely contribution will help ensure that children affected by the crisis can continue learning and access essential nutrition services. In partnership with the Government of Lebanon, UNICEF will support both in-person and remote learning, including through safe learning spaces and community-based programmes, while delivering critical nutrition support to vulnerable children, adolescents, and pregnant and breastfeeding women.
+“On behalf of the Government of the Republic of Korea, we proudly contribute to vital support for nutrition and education programs in Lebanon,” said Gyusuk Geon ambassador of the Republic of Korea in Lebanon. “This is our way of standing shoulder-to-shoulder with the country, affirming that Lebanon does not face these trials alone. Korea stands with Lebanon - today, tomorrow, and always - in shared humanity and unbreakable friendship.”
+“Children in Lebanon cannot afford to lose access to learning or basic nutrition because of this crisis,” said Marcoluigi Corsi, UNICEF Representative in Lebanon. “This contribution from the Republic of Korea comes at a critical time helping children stay in school, stay healthy, and protecting them from the long-term consequences of this emergency.”
+The support will also strengthen access to life-saving nutrition services and promote better child feeding and care practices among families, helping protect children’s growth and development during a period of heightened vulnerability.
+UNICEF welcomes the continued partnership with the Republic of Korea, whose support remains vital in reaching the most vulnerable children and sustaining essential services across Lebanon.
+Media contacts
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:46.692079+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ministry of Public Health and partners call to protect every child through vaccination despite ongoing crisis in Lebanon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/ministry-public-health-and-partners-call-protect-every-child-through-vaccination</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ministry of Public Health and partners call to protect every child through vaccination despite ongoing crisis in Lebanon
+- English
+- العربية
+Beirut, 22 April 2026 - Amid ongoing crises, the Ministry of Public Health (MoPH), together with the European Union, UNICEF, WHO, the Lebanese Red Cross and Gavi, marks World Immunization Week with a renewed call to ensure that every child in Lebanon is protected through routine vaccination.
+The event also marks the official launch of Lebanon’s National Immunization Strategy (NIS), a key milestone led by the Ministry of Public Health to strengthen and sustain immunization services nationwide. The Strategy sets a clear vision to improve vaccination coverage and reinforce the resilience of the national immunization system, ensuring that every child in Lebanon is reached — especially the most vulnerable.
+While the ceasefire offers a critical opportunity for recovery, the impact of the recent escalation continues to affect children and families across the country. Displacement and increased vulnerabilities have placed many children at risk of missing essential vaccinations.
+In this context, immunization remains a cornerstone of child survival and a critical first line of defense against disease outbreaks. Vaccines are among the most effective and cost-efficient public health interventions, protecting children from life-threatening diseases such as measles and polio, especially in fragile and crisis-affected settings.
+“Despite the immense challenges Lebanon continues to face, protecting the health of our children remains a national priority. Immunization is one of the most powerful tools we have to safeguard every child against preventable diseases,” said the Minister of Public Health Dr Rakan Nasereddine. “We are committed to ensuring that vaccination which serve as the entry point to the essential services at the PHC centers, remain accessible to all, especially the most vulnerable, and we call on parents and caregivers to make sure their children are up to date with their vaccines. By working together with our partners, we can protect the future of our children.”
+“Immunization is one of the most effective tools we have to save lives, prevent disease and protect communities,” said Alessandra Viezzer, Head of Cooperation of the EU Delegation to Lebanon. “At a time when Lebanon is facing yet another difficult moment, the European Union is proud to support vaccination efforts and primary healthcare centres across the country. Investing in immunization means investing in stronger health systems, greater stability, and a healthier future for every child”.
+“Families in Lebanon have endured weeks of hardship, displacement and uncertainty and we understand how overwhelming this moment is. But protecting children from preventable diseases is critical,” said Andrea Berther, UNICEF Deputy Representative in Lebanon. “Vaccines save lives and protect children from diseases that can cause severe illness or death. When immunization coverage declines, highly contagious diseases can quickly re-emerge, putting all children at risk.
+"Vaccines have saved more than 150 million lives over the past five decades,” said Dr. Gabriel Novelo Sierra, Health Emergencies Program team lead at WHO Lebanon. “Funding cuts to global health have put these hard-won gains in jeopardy. Outbreaks of vaccine-preventable diseases are increasing around the world, putting lives at risk and exposing countries to increased costs in treating diseases and responding to outbreaks. Countries with limited resources must invest in the highest-impact interventions – and that includes vaccines.”
+Vaccination services continue to be provided free of charge through Primary Health Care Centres (PHCs) across the country, with funding support from the European Union and Gavi. As the backbone of Lebanon’s immunization programme, PHCs serve as the main platform for delivering routine vaccination services nationwide, ensuring continuity of care and access for children and families despite ongoing challenges. Under the leadership of the Ministry of Public Health, efforts are sustained to maintain national coverage and strengthen the resilience of the health system.
+Outreach activities further expand access to vulnerable populations, including displaced families in collective shelters and host communities, through initiatives such as the Ministry’s AaSalameh programme and Primary Healthcare Outreach Units (PHOUs) within UNICEF’s emergency response, helping ensure that no child is left behind.
+In parallel, UNICEF and WHO support the Ministry of Public Health and its partners, including the Lebanese Red Cross, by strengthening cold chain systems, supporting service delivery, and enhancing coordination and monitoring at the national level. These efforts are complemented by expanding access points to vaccination through PHCs, mobile teams, and community outreach activities, contributing to both immediate response needs and longer-term system strengthening.
+As the crisis continues to place additional strain on families and health services, sustained investment in immunization remains essential to prevent disease outbreaks and protect public health. Parents and caregivers are encouraged to review their children’s vaccination records and ensure they are up to date with all recommended doses.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, Twitter, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:50.436312+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UNICEF statement on intensified strikes on Lebanon and the devastating impact on children</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/unicef-statement-intensified-strikes-lebanon-and-devastating-impact-children</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UNICEF statement on intensified strikes on Lebanon and the devastating impact on children
+- English
+- العربية
+NEW YORK, 9 April 2026 – “The intensification of hostilities in Lebanon continues to exact a devastating and inhumane toll on children. In just minutes yesterday, as news of a regional ceasefire agreement briefly ignited hope across the country, deadly Israeli airstrikes struck across Lebanon, reportedly killing 33 children and injuring 153.
+“Children and families faced a wave of bombardments that tore through communities with devastating impact. The latest bloodshed adds to a staggering 600 children either killed or injured in Lebanon since 2 March.
+“UNICEF is receiving reports of children being pulled from under the rubble, while others remain missing and separated from their families. Many are experiencing trauma, having lost loved ones, their homes, and any sense of safety. Across the country, more than one million people have been uprooted, including an estimated 390,000 children, many for the second, third, or even fourth time.
+“International humanitarian law is clear: civilians, including children, must be protected at all times. All parties to the conflict must take all feasible precautions to protect civilians and civilian infrastructure, and ensure safe, sustained, and unimpeded humanitarian access. The use of explosive weapons with wide-area effects in densely populated areas pose a deadly threat for children. They must stop.
+“UNICEF is on the ground in Beirut, treating many injured children under the UNICEF-supported Assistance and Care for War-Wounded and Affected Children (ACWA) programme. As needs surge, UNICEF is scaling up its emergency response. Our teams are helping to deliver essential supplies in shelters, medical supplies to public health facilities, and mobile units provide urgent care to displaced families.
+“While ceasefire efforts elsewhere have brought a measure of relief, as the UN Secretary-General said earlier today, the ongoing military activity in Lebanon poses a grave risk to the ceasefire and the efforts toward a lasting and comprehensive peace in the region. The children in Lebanon cannot be left behind.”
+Media contacts
+Additional resources
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, Twitter, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:52.137249+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>An average of 19,000 children displaced daily as escalating violence uproots 20 per cent of Lebanon's population in three weeks</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/average-19000-children-displaced-daily-escalating-violence-uproots-20-cent-lebanons</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>An average of 19,000 children displaced daily as escalating violence uproots 20 per cent of Lebanon's population in three weeks
+This is a summary of what was said by UNICEF Representative in Lebanon, Marcoluigi Corsi – to whom quoted text may be attributed – at today's press briefing at the Palais des Nations in Geneva
+- English
+- العربية
+BEIRUT, 27 March 2026 – “In just three weeks, more than 370,000 children have been forced out of their homes in Lebanon, an average of at least 19,000 girls and boys displaced every single day. To grasp the scale, this is the equivalent of hundreds of school buses filled with children fleeing for their lives every 24 hours.
+“In less than a single month, roughly 20 per cent of Lebanon’s population has been displaced. The speed and scale are staggering. Across the country, more than one million people are now uprooted—many for the second, third, or even fourth time. This is a sudden, chaotic mass displacement, tearing families apart and hollowing out entire communities, with consequences that will reverberate long after the violence subsides.
+“The mental and emotional exhaustion weighing on the children of Lebanon is devastating. Before having a single moment to heal from the trauma of the last escalation just 15 months ago, they are being violently uprooted all over again. This relentless cycle of bombardment and displacement is severely compounding their psychological scars, embedding deep-seated fear and threatening profound, long-term emotional harm.
+“In a shelter in Beirut, I met 11-year-old Zeinab, who had escaped with her family from the southern suburbs of Beirut to the same school they took refuge in 18 months ago. She told me she never imagined that she would live these days again, sleeping with many people around her and listening to the sound of shelling and bombing almost every night. She just wishes to go back home and go back to school, go back to her normal life.
+“Today, over 135,000 internally displaced persons are seeking refuge in over 660 collective shelters, many of them children. The living conditions are increasingly strained. Many displaced households are sheltering in informal, overcrowded, and unsafe settings, including unfinished buildings, public spaces, and vehicles. Lebanon’s economic crisis and weakened infrastructure were already limiting the country’s ability to respond to basic needs; today, that infrastructure is buckling under the pressure.
+“The essential services that children rely on for their survival and futures are being severely disrupted. In areas like Bekaa and Baalbek, bombardments have destroyed vital water reservoirs and pumping stations, cutting off tens of thousands of individuals from safe water. Furthermore, with an estimated 435 public schools now functioning as shelters, the education of over 115,000 students has been abruptly halted.
+“The human cost of this escalation is shocking. To date, at least 121 children have been killed, and 395 have been injured. Those who survive the bombardment are waking up to a dire humanitarian reality. We are seeing families fleeing with only the clothes on their backs, forced to move multiple times within days as repeated displacement orders are issued.
+“Meanwhile, essential civilian infrastructure - including hospitals, schools, bridges and water and sanitation systems – upon which children depend to carry on with their lives have been consistently attacked, damaged, or destroyed.
+“UNICEF is on the ground, working around the clock alongside our partners and national systems to support children on the move, in shelters, and in hard-to-reach areas. In just the past few weeks, our Rapid Response Mechanism has reached over 167,000 displaced people with essential non-food items and winterization kits.
+“We have delivered more than 140 tons of essential medical supplies to hospitals and activated 40 Primary Healthcare Satellite Units to ensure children and families in shelters have access to care. We are delivering emergency water and sanitation support to nearly 190 shelters, and we are working to protect children’s futures by supporting the Ministry of Education in establishing online learning access and planning Temporary Learning Spaces.
+“However, humanitarian assistance alone cannot solve this crisis. Our emergency response capacity is severely weakened by repeated attacks on paramedics and health workers, and thousands of families remain cut off in hard-to-reach areas due to safety concerns and lack of transport.
+“Children are paying the highest price for this conflict. We urgently call for unimpeded humanitarian access to all those in need. We call for an immediate end to attacks on civilian infrastructure—including schools, hospitals, and water systems. Above all, the 370,000 displaced children desperately need an immediate ceasefire. They need to stop running and start living as children should.”
+Media contacts
+Additional resources
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, Twitter, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:53.911544+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNICEF delivers emergency medical supplies as hospitals in Lebanon struggle to cope with rising casualties</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/unicef-delivers-emergency-medical-supplies-hospitals-lebanon-struggle-cope-rising</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UNICEF delivers emergency medical supplies as hospitals in Lebanon struggle to cope with rising casualties
+- English
+- العربية
+Beirut, 18 March 2026 – As hostilities continue to escalate across Lebanon, UNICEF has delivered a new shipment of 32,5 metric tons of emergency medical supplies to support hospitals and frontline health services overwhelmed by the rising number of casualties, including children.
+According to the Ministry of Public Health, at least 116 children have been killed and more than 356 injured since the beginning of the escalation, with overall casualties continuing to rise. Hospitals and emergency health services are under immense strain as they work to treat the growing number of wounded patients while maintaining essential care.
+The latest shipment, transported through a UNICEF charter, includes critical medical supplies to support hospitals, primary healthcare centres and mobile Primary Healthcare Satellite Units (PSUs) providing frontline care to affected populations. These supplies are essential to sustain lifesaving services, including trauma care, maternal and newborn services, and the treatment of acute and infectious conditions.
+“Hospitals are overwhelmed, and without urgent support, the ability to provide lifesaving care to children will be at serious risk. These supplies are critical to ensure that every injured child has a chance to receive the care they need”, said Ted Chaiban, UNICEF Deputy Executive Director for Emergencies and Supply Operations.
+UNICEF is working closely with the Ministry of Public Health and partners to support Lebanon’s health system at a time of rapidly increasing needs. This includes the delivery of essential medicines and medical supplies, support to hospitals and intensive care units, and the expansion of mobile Primary Healthcare Satellite Units to reach displaced populations in shelters and hard-to-reach areas.
+To date, UNICEF has supported the activation of dozens of mobile health teams and primary healthcare centres, providing essential services including consultations, vaccination, nutrition screening, and emergency care for children and families affected by the crisis. UNICEF is also supporting neonatal and pediatric intensive care services in public hospitals to ensure that the most vulnerable children receive specialized treatment.
+Beyond medical supplies, UNICEF has delivered 800 metric tons of emergency relief items across Lebanon since 2 March, reaching around 150,000 people. This includes internally displaced people in approximately 250 shelters, as well as those in hard-to-reach areas and others on the move across the country. Essential relief items include about 600,000 liters of water, 2,000 blankets, mattresses and sleeping bags, 11,000 winter kits, 40,000 family hygiene and baby kits and 11,000 personal hygiene kits for women and adolescent girls. Medical, mental health and psychosocial support services are also being rolled out at shelters.
+UNICEF reiterates its call for the protection of civilians, especially children, and for safe and sustained humanitarian access to deliver lifesaving assistance. Immediate support from the international community is critical to sustain health services and ensure that children in Lebanon receive the care and protection they urgently need.
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, Twitter, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:58:55.600802+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UNICEF_Lebanon.xlsx
+++ b/UNICEF_Lebanon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1084,6 +1084,52 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Young people help shape Lebanon’s National Youth Strategy 2026–2030</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/lebanon/press-releases/young-people-help-shape-lebanons-national-youth-strategy-20262030</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Young people help shape Lebanon’s National Youth Strategy 2026–2030
+The Ministry of Youth and Sports, UNICEF and UNFPA advance national dialogue to ensure young people’s priorities and aspirations inform policies and opportunities for their future
+- English
+- العربية
+Tripoli, 28 October 2026 – Young people from across North Lebanon, including universities, community centers, NGOs ,and vocational institutes came together to share their priorities, experiences and solutions as part of the second national consultation and the first regional consultations on Lebanon’s National Youth Strategy 2026–2030, led by the Ministry of Youth and Sports in partnership with UNICEF and UNFPA.
+Building on the national consultation process launched in February 2026, which was temporarily suspended due to the security situation; discussions have now resumed to ensure that the Strategy reflects the diverse realities and aspirations of young people at national level and provides a framework for coordinated national action to strengthen their opportunities, participation and well-being.
+Lebanon’s young people continue to face significant challenges, including disruptions to education, limited access to decent employment and the impact of successive crises. Yet they also play an essential role in supporting their communities, driving innovation and contributing to social cohesion and recovery.
+The consultations provide a platform for young people to identify priorities and propose solutions across key areas, including education and skills, employment and entrepreneurship, health and well-being including Sexual and reproductive health and rights, responsible digital engagement and artificial intelligence, environmental sustainability, active citizenship, peace and social cohesion.
+H.E. Dr. Nora Bayrakdarian, Minister of Youth and Sports:
+“A National Youth Strategy must be built on the priorities and aspirations of young people themselves. Through these consultations, we are strengthening their participation in shaping a national framework that responds to their needs and expands their opportunities. Our responsibility is to ensure that their contributions translate into clear priorities, coordinated action and meaningful progress”.
+H.E Dr. Rima Karame , Minister of Education and Higher Education “Student voice is not an addition to education. It is one of the ways young people learn citizenship: That they have a right to be heard, but also a responsibility to contribute.”.
+“Young people are not only the future of Lebanon. They are already contributing to its recovery, development, and resilience. Their participation in shaping national policies is a right, and an essential condition for making those policies more relevant, inclusive and effective,” said Marcoluigi Corsi, UNICEF Representative in Lebanon. “UNICEF is committed to supporting a Strategy that invests in young people’s skills, well-being and opportunities, while ensuring that their voices continue to inform decisions and actions that affect their lives.”
+“Young people will be front and central to design, develop and implement the National Youth Strategy. Key priorities that the young people of Lebanon have asked for include their safety, security, protection, and health including sexual and reproductive health mental health support,” said Anandita Philipose. “UNFPA is committed to supporting the Ministry of Youth and Sports and our partners to translate these priorities into practical action, with and young people.”
+“We are proud to host the second round of consultations for the National Youth Strategy 2026-2023 on our main campus here in Tripoli” - Dr. Bilal Barke representing the President of the Lebanese University Dr. Bassam Badran.
+The consultations form part of a broader national effort to develop an inclusive, evidence-informed and actionable Youth Strategy, bringing together young people, public institutions and partners across sectors.
+The priorities and recommendations emerging from these discussions will inform the finalization of the National Youth Strategy 2026–2030, with a shared emphasis on translating young people's contributions into concrete actions and sustained engagement during implementation.
+The Minister of Youth and Sports closed the session by: “We are here today to listen to you because your opinions and ideas matter to us. The doors of the Ministry of Youth and Sports are open to all young women and men in Lebanon.”
+About UNICEF
+UNICEF works in some of the world’s toughest places, to reach the world’s most disadvantaged children. Across 190 countries and territories, we work for every child, everywhere, to build a better world for everyone. For more information about UNICEF and its work for children visit www.unicef.org/lebanon/.
+Follow UNICEF Lebanon on Facebook, X, Instagram, LinkedIn, YouTube and TikTok.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:37:20.820944+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UNICEF_Lebanon.xlsx
+++ b/UNICEF_Lebanon.xlsx
@@ -414,7 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
